--- a/docs/Capg_Project_Section1.xlsx
+++ b/docs/Capg_Project_Section1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Desktop\capg_project_sec2\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6130CA28-05E4-4054-B6DC-420330F75A2B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B04EFF-02B3-4277-8080-231075340096}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6230" firstSheet="3" activeTab="7" xr2:uid="{0D2F8E87-414D-43FE-9E16-A3E109D6CAA9}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6230" xr2:uid="{0D2F8E87-414D-43FE-9E16-A3E109D6CAA9}"/>
   </bookViews>
   <sheets>
     <sheet name="Guidance &amp; Instructions" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="297">
   <si>
     <t>1. TEST PLAN</t>
   </si>
@@ -904,6 +904,36 @@
   </si>
   <si>
     <t>Project Information</t>
+  </si>
+  <si>
+    <t>Validate successful UI login functionality</t>
+  </si>
+  <si>
+    <t>Validate note creation through UI</t>
+  </si>
+  <si>
+    <t>Validate created note appears instantly in UI list</t>
+  </si>
+  <si>
+    <t>Validate GET /notes API returns notes list and response time</t>
+  </si>
+  <si>
+    <t>Validate UI-created note exists in API response</t>
+  </si>
+  <si>
+    <t>Validate note deletion through API</t>
+  </si>
+  <si>
+    <t>Validate API-deleted note disappears from UI</t>
+  </si>
+  <si>
+    <t>Validate API performance and response timing</t>
+  </si>
+  <si>
+    <t>Validate negative UI and API scenarios</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
 </sst>
 </file>
@@ -2327,6 +2357,7 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="52.6328125" customWidth="1"/>
+    <col min="4" max="4" width="42.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2465,6 +2496,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEDD8516-926F-4179-854C-5A1080957024}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" width="49.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="13" t="s">
@@ -2630,7 +2664,7 @@
     <col min="1" max="1" width="20.7265625" customWidth="1"/>
     <col min="2" max="2" width="18.54296875" customWidth="1"/>
     <col min="3" max="3" width="15.36328125" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" customWidth="1"/>
+    <col min="4" max="4" width="51.6328125" customWidth="1"/>
     <col min="5" max="5" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2661,6 +2695,12 @@
       <c r="C2" s="15" t="s">
         <v>260</v>
       </c>
+      <c r="D2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E2" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
@@ -2672,6 +2712,12 @@
       <c r="C3" s="15" t="s">
         <v>261</v>
       </c>
+      <c r="D3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
@@ -2683,6 +2729,12 @@
       <c r="C4" s="15" t="s">
         <v>262</v>
       </c>
+      <c r="D4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E4" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
@@ -2694,6 +2746,12 @@
       <c r="C5" s="15" t="s">
         <v>139</v>
       </c>
+      <c r="D5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
@@ -2705,6 +2763,12 @@
       <c r="C6" s="15" t="s">
         <v>140</v>
       </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E6" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
@@ -2716,6 +2780,12 @@
       <c r="C7" s="15" t="s">
         <v>141</v>
       </c>
+      <c r="D7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
@@ -2727,6 +2797,12 @@
       <c r="C8" s="15" t="s">
         <v>142</v>
       </c>
+      <c r="D8" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
@@ -2738,6 +2814,12 @@
       <c r="C9" s="15" t="s">
         <v>139</v>
       </c>
+      <c r="D9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
@@ -2748,6 +2830,12 @@
       </c>
       <c r="C10" s="15" t="s">
         <v>143</v>
+      </c>
+      <c r="D10" t="s">
+        <v>295</v>
+      </c>
+      <c r="E10" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
